--- a/LISTAS/ma/FRATACHO ALGARROBO.xlsx
+++ b/LISTAS/ma/FRATACHO ALGARROBO.xlsx
@@ -725,14 +725,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="26" t="n">
-        <v>45163.60879721135</v>
+        <v>45219</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="19">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -778,26 +774,6 @@
       </c>
       <c r="E11" s="10" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="19">
       <c r="A32" s="13" t="inlineStr">
         <is>
@@ -829,7 +805,7 @@
       </c>
       <c r="C33" s="21" t="n"/>
       <c r="D33" s="15" t="n">
-        <v>895.804</v>
+        <v>954.2</v>
       </c>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="16" t="n"/>
@@ -847,7 +823,7 @@
       </c>
       <c r="C34" s="21" t="n"/>
       <c r="D34" s="15" t="n">
-        <v>1037.9</v>
+        <v>1200</v>
       </c>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="16" t="n"/>
@@ -865,7 +841,7 @@
       </c>
       <c r="C35" s="21" t="n"/>
       <c r="D35" s="15" t="n">
-        <v>1157.74</v>
+        <v>1231.1</v>
       </c>
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="16" t="n"/>
@@ -883,7 +859,7 @@
       </c>
       <c r="C36" s="21" t="n"/>
       <c r="D36" s="15" t="n">
-        <v>1296.84</v>
+        <v>1378</v>
       </c>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="16" t="n"/>
@@ -901,18 +877,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
     <row r="52" ht="15.75" customHeight="1" s="19">
       <c r="A52" s="5" t="n"/>
     </row>
@@ -921,16 +885,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="A38:D38"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/FRATACHO ALGARROBO.xlsx
+++ b/LISTAS/ma/FRATACHO ALGARROBO.xlsx
@@ -725,7 +725,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="26" t="n">
-        <v>45219</v>
+        <v>45252</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>
@@ -885,16 +885,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/FRATACHO ALGARROBO.xlsx
+++ b/LISTAS/ma/FRATACHO ALGARROBO.xlsx
@@ -725,7 +725,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="26" t="n">
-        <v>45252</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>
@@ -885,16 +885,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A38:D38"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/FRATACHO ALGARROBO.xlsx
+++ b/LISTAS/ma/FRATACHO ALGARROBO.xlsx
@@ -725,7 +725,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="26" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>
@@ -885,16 +885,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/FRATACHO ALGARROBO.xlsx
+++ b/LISTAS/ma/FRATACHO ALGARROBO.xlsx
@@ -725,7 +725,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="26" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>

--- a/LISTAS/ma/FRATACHO ALGARROBO.xlsx
+++ b/LISTAS/ma/FRATACHO ALGARROBO.xlsx
@@ -725,10 +725,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="26" t="n">
-        <v>45266</v>
+        <v>45225.50783624935</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="19">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -774,6 +778,26 @@
       </c>
       <c r="E11" s="10" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="19">
       <c r="A32" s="13" t="inlineStr">
         <is>
@@ -805,7 +829,7 @@
       </c>
       <c r="C33" s="21" t="n"/>
       <c r="D33" s="15" t="n">
-        <v>954.2</v>
+        <v>1069</v>
       </c>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="16" t="n"/>
@@ -823,7 +847,7 @@
       </c>
       <c r="C34" s="21" t="n"/>
       <c r="D34" s="15" t="n">
-        <v>1200</v>
+        <v>1237.6</v>
       </c>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="16" t="n"/>
@@ -841,7 +865,7 @@
       </c>
       <c r="C35" s="21" t="n"/>
       <c r="D35" s="15" t="n">
-        <v>1231.1</v>
+        <v>1378</v>
       </c>
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="16" t="n"/>
@@ -859,7 +883,7 @@
       </c>
       <c r="C36" s="21" t="n"/>
       <c r="D36" s="15" t="n">
-        <v>1378</v>
+        <v>1544</v>
       </c>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="16" t="n"/>
@@ -877,6 +901,18 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
     <row r="52" ht="15.75" customHeight="1" s="19">
       <c r="A52" s="5" t="n"/>
     </row>
@@ -885,16 +921,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/FRATACHO ALGARROBO.xlsx
+++ b/LISTAS/ma/FRATACHO ALGARROBO.xlsx
@@ -725,14 +725,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="26" t="n">
-        <v>45225.50783624935</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="7" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="19">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -778,26 +774,6 @@
       </c>
       <c r="E11" s="10" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="19">
       <c r="A32" s="13" t="inlineStr">
         <is>
@@ -829,7 +805,7 @@
       </c>
       <c r="C33" s="21" t="n"/>
       <c r="D33" s="15" t="n">
-        <v>1069</v>
+        <v>954.2</v>
       </c>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="16" t="n"/>
@@ -847,7 +823,7 @@
       </c>
       <c r="C34" s="21" t="n"/>
       <c r="D34" s="15" t="n">
-        <v>1237.6</v>
+        <v>1200</v>
       </c>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="16" t="n"/>
@@ -865,7 +841,7 @@
       </c>
       <c r="C35" s="21" t="n"/>
       <c r="D35" s="15" t="n">
-        <v>1378</v>
+        <v>1231.1</v>
       </c>
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="16" t="n"/>
@@ -883,7 +859,7 @@
       </c>
       <c r="C36" s="21" t="n"/>
       <c r="D36" s="15" t="n">
-        <v>1544</v>
+        <v>1378</v>
       </c>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="16" t="n"/>
@@ -901,18 +877,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
     <row r="52" ht="15.75" customHeight="1" s="19">
       <c r="A52" s="5" t="n"/>
     </row>
@@ -921,16 +885,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="A38:D38"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
